--- a/seia-variables.xlsx
+++ b/seia-variables.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t xml:space="preserve">Variable Clave</t>
   </si>
@@ -28,7 +28,7 @@
     <t xml:space="preserve">Justificación Analítica</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordenadas UTM/Geográficas (polígono)</t>
+    <t xml:space="preserve">Coordenadas UTM/Geográficas (punto representativo)</t>
   </si>
   <si>
     <t xml:space="preserve">Permite evaluar distribución territorial, superposición con áreas protegidas y análisis espacial de impactos. Exigible por SEA.</t>
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Características del generador</t>
   </si>
   <si>
-    <t xml:space="preserve">Aerogenerador: potencia unitaria, altura de buje, diámetro de rotor. FV: tipo de módulo, sistema de seguimiento, tipo de inversor.</t>
+    <t xml:space="preserve">Eólica: potencia unitaria del aerogenerador, altura de buje, diámetro de rotor. Fotovoltaica: tipo de módulo, sistema de seguimiento, tipo de inversor.</t>
   </si>
   <si>
     <t xml:space="preserve">Emisiones GEI embebidas (kg CO2-eq kWh-1)</t>
@@ -112,10 +112,13 @@
     <t xml:space="preserve">Exigido por SEA para operación. Los papers lo cuantifican por ACV y permiten comparación inter-tecnológica.</t>
   </si>
   <si>
-    <t xml:space="preserve">Emisiones MP10 y MP2.5 (t año-1)</t>
+    <t xml:space="preserve">Emisiones MP10 (t año-1)</t>
   </si>
   <si>
     <t xml:space="preserve">Exigido por SEA en fase de construcción. Relevante en zonas áridas por erosión eólica y transporte de polvo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emisiones MP2.5 (t año-1)</t>
   </si>
 </sst>
 </file>
@@ -130,6 +133,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -209,8 +213,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -242,37 +250,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -345,138 +353,146 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.38"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>31</v>
       </c>
     </row>
